--- a/data/trans_orig/P64S_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P64S_2023_R-Edad-trans_orig.xlsx
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>21473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2116,32 +2116,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2151,32 +2151,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17450</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30332</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -2194,32 +2194,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45352</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59440</t>
+          <t>59736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2229,32 +2229,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37320</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48801</t>
+          <t>53509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2264,32 +2264,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>82672</t>
+          <t>84750</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>66221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101753</t>
+          <t>106625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -2307,32 +2307,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2377,32 +2377,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -2420,32 +2420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2455,32 +2455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>33865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2490,32 +2490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57950</t>
+          <t>66473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23824</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36040</t>
+          <t>36442</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>37451</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24365</t>
+          <t>26389</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52406</t>
+          <t>50815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19745</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>23826</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3554,32 +3554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3589,32 +3589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3624,32 +3624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>24572</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3780,32 +3780,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35374</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3815,32 +3815,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>46264</t>
+          <t>52958</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -3893,32 +3893,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3928,32 +3928,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3963,32 +3963,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4006,32 +4006,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4041,32 +4041,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4076,32 +4076,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>29060</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -4119,32 +4119,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>238788</t>
+          <t>262148</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>213986</t>
+          <t>236847</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>259635</t>
+          <t>286826</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4154,32 +4154,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>148945</t>
+          <t>159594</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>73882</t>
+          <t>142594</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>194698</t>
+          <t>179136</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4189,32 +4189,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>387733</t>
+          <t>421743</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>265706</t>
+          <t>390703</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>442443</t>
+          <t>453585</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -4267,32 +4267,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>215953</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4302,32 +4302,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>249148</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>48604</t>
+          <t>57936</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>41354</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>77676</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4380,32 +4380,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>64810</t>
+          <t>74008</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>60733</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>89550</t>
+          <t>91582</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>113414</t>
+          <t>131944</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>82455</t>
+          <t>107887</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>139208</t>
+          <t>155815</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>349720</t>
+          <t>315119</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>349720</t>
+          <t>315119</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>349720</t>
+          <t>315119</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,17 +4528,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>700063</t>
+          <t>711040</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>700063</t>
+          <t>711040</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>700063</t>
+          <t>711040</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>28725</t>
+          <t>33904</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20463</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>47017</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>32678</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36275</t>
+          <t>41860</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>56229</t>
+          <t>66582</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>44706</t>
+          <t>53536</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69604</t>
+          <t>82803</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23443</t>
+          <t>27158</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,32 +4949,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,32 +4984,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>26872</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>38909</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>672</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>672</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5479,22 +5479,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5514,32 +5514,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5549,32 +5549,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5592,32 +5592,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5662,32 +5662,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5705,32 +5705,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>28812</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5740,32 +5740,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5775,32 +5775,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>39340</t>
+          <t>50253</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5888,17 +5888,17 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5931,32 +5931,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5966,32 +5966,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>27025</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6001,32 +6001,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>33450</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>23891</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -6044,32 +6044,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>314892</t>
+          <t>357542</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>295311</t>
+          <t>334577</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>336555</t>
+          <t>381194</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>195154</t>
+          <t>213906</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>180494</t>
+          <t>198091</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>210168</t>
+          <t>231132</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6114,32 +6114,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>510046</t>
+          <t>571448</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>484770</t>
+          <t>540263</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>534203</t>
+          <t>599292</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -6157,32 +6157,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6192,32 +6192,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6227,32 +6227,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>20883</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -6270,102 +6270,102 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>52819</t>
+          <t>62559</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>79863</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>94754</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>81071</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>109719</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>20,42%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>157314</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>136319</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>178082</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
           <t>14,6%</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>83670</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>71869</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>97676</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>23,82%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>136490</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>119368</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>157733</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>16,78%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -6383,17 +6383,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>461966</t>
+          <t>536496</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>461966</t>
+          <t>536496</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>461966</t>
+          <t>536496</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>351206</t>
+          <t>396999</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>351206</t>
+          <t>396999</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>351206</t>
+          <t>396999</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6453,17 +6453,17 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>813172</t>
+          <t>933495</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>813172</t>
+          <t>933495</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>813172</t>
+          <t>933495</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -6726,32 +6726,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>32168</t>
+          <t>34294</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>52984</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>36356</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>28468</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>65122</t>
+          <t>70651</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>87870</t>
+          <t>84797</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -6839,32 +6839,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6874,32 +6874,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>41311</t>
+          <t>26222</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6909,32 +6909,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>28944</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>46231</t>
+          <t>39448</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>692</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -7404,32 +7404,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7474,32 +7474,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>39855</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7552,67 +7552,67 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>4206</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>9019</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>4160</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="T64" s="2" t="inlineStr">
-        <is>
-          <t>10318</t>
-        </is>
-      </c>
-      <c r="U64" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V64" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -7630,32 +7630,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26482</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7665,32 +7665,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7700,32 +7700,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>34061</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>43258</t>
+          <t>45313</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>856</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>706</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -7856,32 +7856,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7891,32 +7891,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>26890</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>43080</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -7969,32 +7969,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>598525</t>
+          <t>378020</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>519137</t>
+          <t>356153</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>687680</t>
+          <t>399532</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8004,32 +8004,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>251904</t>
+          <t>235883</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>227050</t>
+          <t>218531</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>296098</t>
+          <t>252084</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8039,32 +8039,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>850428</t>
+          <t>613904</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>746457</t>
+          <t>585086</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>1023614</t>
+          <t>642420</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -8082,32 +8082,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8117,32 +8117,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8152,32 +8152,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -8195,32 +8195,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>66187</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>96124</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8230,32 +8230,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>94413</t>
+          <t>101004</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>71475</t>
+          <t>88046</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>110177</t>
+          <t>116958</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8265,32 +8265,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>154260</t>
+          <t>167191</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>76859</t>
+          <t>147350</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>203187</t>
+          <t>189831</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -8308,17 +8308,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>745082</t>
+          <t>543550</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>745082</t>
+          <t>543550</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>745082</t>
+          <t>543550</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8343,17 +8343,17 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>452884</t>
+          <t>454985</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>452884</t>
+          <t>454985</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>452884</t>
+          <t>454985</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8378,17 +8378,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>1197966</t>
+          <t>998535</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>1197966</t>
+          <t>998535</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>1197966</t>
+          <t>998535</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8651,32 +8651,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>20143</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>29330</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8686,32 +8686,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8721,32 +8721,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>42648</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>54528</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -8764,32 +8764,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8799,22 +8799,22 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8834,32 +8834,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>16997</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>29695</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -9329,32 +9329,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9364,32 +9364,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9399,32 +9399,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -9555,32 +9555,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9590,32 +9590,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9625,32 +9625,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -9668,32 +9668,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9738,32 +9738,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -9781,32 +9781,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9816,32 +9816,32 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9851,32 +9851,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -9894,32 +9894,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>183727</t>
+          <t>197220</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>167805</t>
+          <t>179614</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>198686</t>
+          <t>214840</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>85918</t>
+          <t>94020</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>74515</t>
+          <t>82400</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>96605</t>
+          <t>106270</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9964,32 +9964,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>269645</t>
+          <t>291239</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>250929</t>
+          <t>269762</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>289595</t>
+          <t>311478</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -10007,32 +10007,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>708</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10077,32 +10077,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -10120,32 +10120,32 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>50343</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>39962</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>69228</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10155,27 +10155,27 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>64641</t>
+          <t>71814</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>54625</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>74122</t>
+          <t>82873</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10190,32 +10190,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>114984</t>
+          <t>125966</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>98255</t>
+          <t>108164</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>131373</t>
+          <t>144402</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -10233,17 +10233,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10268,17 +10268,17 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>208136</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>208136</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>208136</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10303,17 +10303,17 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>507274</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>507274</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>507274</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10611,32 +10611,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>295</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10646,32 +10646,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>569</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>569</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>816</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>816</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
@@ -11334,12 +11334,12 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -11525,12 +11525,12 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11550,32 +11550,32 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
@@ -11673,12 +11673,12 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -11741,32 +11741,32 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>432</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11776,32 +11776,32 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>442</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -11819,32 +11819,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11854,32 +11854,32 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11889,32 +11889,32 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
@@ -12012,12 +12012,12 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -12045,32 +12045,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12080,32 +12080,32 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12115,32 +12115,32 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -12158,17 +12158,17 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12193,17 +12193,17 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12228,17 +12228,17 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -13754,12 +13754,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
@@ -13824,12 +13824,12 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="V119" s="2" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S121" s="2" t="inlineStr">
@@ -14050,12 +14050,12 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U121" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="V121" s="2" t="inlineStr">
@@ -14083,17 +14083,17 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -14153,17 +14153,17 @@
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U122" s="2" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -14210,12 +14210,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S123" s="2" t="inlineStr">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V123" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="S124" s="2" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="U124" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="W124" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -14426,32 +14426,32 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>97671</t>
+          <t>107756</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>66013</t>
+          <t>87536</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>120127</t>
+          <t>130195</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -14461,32 +14461,32 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>114299</t>
+          <t>125338</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>94451</t>
+          <t>109454</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>134275</t>
+          <t>143610</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -14496,32 +14496,32 @@
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>211970</t>
+          <t>233094</t>
         </is>
       </c>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>165956</t>
+          <t>207429</t>
         </is>
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>244327</t>
+          <t>264447</t>
         </is>
       </c>
       <c r="U125" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -14539,32 +14539,32 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>53654</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>27291</t>
+          <t>39921</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>70517</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -14574,32 +14574,32 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>56614</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>43192</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>67387</t>
+          <t>70042</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -14609,32 +14609,32 @@
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>91230</t>
+          <t>110268</t>
         </is>
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>69560</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>117304</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="U127" s="2" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="W127" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S128" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V128" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -14878,32 +14878,32 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -14948,32 +14948,32 @@
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="U129" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V130" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -15104,32 +15104,32 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>29229</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>50689</t>
+          <t>60072</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -15139,32 +15139,32 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -15174,32 +15174,32 @@
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>71392</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="S131" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>63283</t>
         </is>
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>91355</t>
+          <t>101484</t>
         </is>
       </c>
       <c r="U131" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -15217,32 +15217,32 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -15252,22 +15252,22 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -15287,32 +15287,32 @@
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -15330,32 +15330,32 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>71450</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>46745</t>
+          <t>65642</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>95671</t>
+          <t>106185</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -15365,32 +15365,32 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>50729</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t>47487</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>65870</t>
+          <t>75552</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15400,32 +15400,32 @@
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>122179</t>
+          <t>144795</t>
         </is>
       </c>
       <c r="S133" s="2" t="inlineStr">
         <is>
-          <t>93526</t>
+          <t>123646</t>
         </is>
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>174738</t>
         </is>
       </c>
       <c r="U133" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V133" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W133" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -15443,32 +15443,32 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -15478,32 +15478,32 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -15513,32 +15513,32 @@
       </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>24280</t>
+          <t>33516</t>
         </is>
       </c>
       <c r="U134" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -15556,32 +15556,32 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>44762</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>63550</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -15591,32 +15591,32 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>63967</t>
+          <t>76627</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>61558</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>81174</t>
+          <t>92663</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -15626,32 +15626,32 @@
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>110861</t>
+          <t>136805</t>
         </is>
       </c>
       <c r="S135" s="2" t="inlineStr">
         <is>
-          <t>85866</t>
+          <t>113176</t>
         </is>
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>136866</t>
+          <t>161836</t>
         </is>
       </c>
       <c r="U135" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -15669,32 +15669,32 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1387284</t>
+          <t>1245691</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1289471</t>
+          <t>1200853</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>1582215</t>
+          <t>1290981</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -15704,32 +15704,32 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>724227</t>
+          <t>750324</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>613242</t>
+          <t>710437</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>781422</t>
+          <t>786010</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -15739,32 +15739,32 @@
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>2111512</t>
+          <t>1996016</t>
         </is>
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>1957840</t>
+          <t>1935581</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>2372491</t>
+          <t>2050118</t>
         </is>
       </c>
       <c r="U136" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -15782,32 +15782,32 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>47174</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -15817,32 +15817,32 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>77693</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>298378</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -15852,32 +15852,32 @@
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
-          <t>94950</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>369812</t>
+          <t>65591</t>
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -15895,32 +15895,32 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>240393</t>
+          <t>275103</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>169556</t>
+          <t>242433</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>287713</t>
+          <t>311849</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -15930,32 +15930,32 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>333866</t>
+          <t>371242</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>282811</t>
+          <t>342012</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>367794</t>
+          <t>399615</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -15965,32 +15965,32 @@
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
-          <t>574258</t>
+          <t>646345</t>
         </is>
       </c>
       <c r="S138" s="2" t="inlineStr">
         <is>
-          <t>441969</t>
+          <t>598013</t>
         </is>
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>642717</t>
+          <t>691441</t>
         </is>
       </c>
       <c r="U138" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -16008,17 +16008,17 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16043,17 +16043,17 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -16078,17 +16078,17 @@
       </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="S139" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="U139" s="2" t="inlineStr">
